--- a/artfynd/A 18031-2026 artfynd.xlsx
+++ b/artfynd/A 18031-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -951,118 +951,6 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>134233288</v>
-      </c>
-      <c r="B4" t="n">
-        <v>8460</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Gräsbergsbrännan , Dlr</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>544243</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6765337</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Enviken</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vildbränna från 2020.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18031-2026 artfynd.xlsx
+++ b/artfynd/A 18031-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -951,6 +951,118 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134233288</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gräsbergsbrännan , Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>544243</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6765337</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Enviken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vildbränna från 2020.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18031-2026 artfynd.xlsx
+++ b/artfynd/A 18031-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -811,6 +816,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134231505</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -950,6 +960,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232004</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,8 +1077,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134233288</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 18031-2026 artfynd.xlsx
+++ b/artfynd/A 18031-2026 artfynd.xlsx
@@ -971,7 +971,7 @@
         <v>134233288</v>
       </c>
       <c r="B4" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18031-2026 artfynd.xlsx
+++ b/artfynd/A 18031-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,54 +680,66 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134233288</v>
+        <v>134231505</v>
       </c>
       <c r="B2" t="n">
-        <v>8461</v>
+        <v>4662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>101849</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Slät tallkapuschongbagge</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Stephanopachys linearis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(Kugelann, 1792)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gräsbergsbrännan , Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544243</v>
+        <v>544322</v>
       </c>
       <c r="R2" t="n">
-        <v>6765337</v>
+        <v>6765110</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +776,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Vildbränna från 2020.</t>
+          <t>I brandskadad 50-årig tall med kraftiga brandljud, vildbränna från 2020.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +789,21 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -790,6 +817,267 @@
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134231505</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134232004</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4662</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>101849</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Slät tallkapuschongbagge</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Stephanopachys linearis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Kugelann, 1792)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gräsbergsbrännan , Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>544367</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6765250</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Enviken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I brandskadad 50-årig tall med kraftiga brandljud, vildbränna från 2020.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232004</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134233288</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gräsbergsbrännan , Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>544243</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6765337</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Enviken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vildbränna från 2020.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134233288</t>
         </is>
@@ -798,6 +1086,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18031-2026 artfynd.xlsx
+++ b/artfynd/A 18031-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134231505</v>
       </c>
       <c r="B2" t="n">
-        <v>4662</v>
+        <v>4663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>134232004</v>
       </c>
       <c r="B3" t="n">
-        <v>4662</v>
+        <v>4663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
